--- a/  диограмма 21 мая xlsx.xlsx
+++ b/  диограмма 21 мая xlsx.xlsx
@@ -56,12 +56,12 @@
     <t>медиана</t>
   </si>
   <si>
+    <t>мода</t>
+  </si>
+  <si>
     <t>дисперсия</t>
   </si>
   <si>
-    <t>мода</t>
-  </si>
-  <si>
     <t>колледж 1</t>
   </si>
   <si>
@@ -70,13 +70,13 @@
   <si>
     <t>колледж 2</t>
   </si>
+  <si>
+    <t>колледж 3</t>
+  </si>
+  <si>
+    <t>колледж 4</t>
+  </si>
   <si/>
-  <si>
-    <t>колледж 3</t>
-  </si>
-  <si>
-    <t>колледж 4</t>
-  </si>
 </sst>
 </file>
 
@@ -1531,7 +1531,7 @@
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="e">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">_XLFN.MODE.SNGL('Лист3'!A2:A25)</f>
@@ -1548,7 +1548,7 @@
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">_XLFN.VAR.S('Лист3'!A2:A25)</f>
@@ -1655,7 +1655,7 @@
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3211400</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4961201</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row outlineLevel="0" r="19">
       <c r="L19" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
